--- a/logs/result.xlsx
+++ b/logs/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,6 +1273,270 @@
         <v>0.0014</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dinov3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:31:17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>uliege</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>/home/labsig/Documents/Axelle/Main research/Data/uliege/validation</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8966</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8953</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9478</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9657</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8976</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="O14" t="n">
+        <v>607.1082</v>
+      </c>
+      <c r="P14" t="n">
+        <v>508.1221</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>88.89619999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.8078</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dinov3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-01 13:12:59</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uliege</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>/home/labsig/Documents/Axelle/Main research/Data/uliege/validation</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9171</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7454</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9325</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="O15" t="n">
+        <v>963.8732</v>
+      </c>
+      <c r="P15" t="n">
+        <v>834.0479</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>120.3093</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.6666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dinov3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-01 13:47:23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>uliege</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>/home/labsig/Documents/Axelle/Main research/Data/uliege/validation</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7367</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9302</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9334</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7516</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9301</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.9338</v>
+      </c>
+      <c r="O16" t="n">
+        <v>930.8831</v>
+      </c>
+      <c r="P16" t="n">
+        <v>806.4645</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>115.5109</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.5014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dinov3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-01 14:41:47</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>uliege</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>/home/labsig/Documents/Axelle/Main research/Data/uliege/validation</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6608000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8672</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6348</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7786</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="O17" t="n">
+        <v>930.0884</v>
+      </c>
+      <c r="P17" t="n">
+        <v>805.3756</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>115.9474</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.4539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
